--- a/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 5_Spesialis.xlsx
+++ b/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 5_Spesialis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\titipan Feli\PROYEK GEDE\Database\Template Baru kosong\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\z\TemplateJobDescBaruKosongan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64B6E19-6FD1-4586-9FDB-28675415E890}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96590A7-EA7E-46E8-9FDA-FC8D7E60D624}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{B4CA32BC-DA9F-4539-8D41-F96D4CBDAEFA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>JOB DESCRIPTION</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Memahami secara baik tentang sasaran dan operasi bisnis PT.</t>
-  </si>
-  <si>
-    <t>Untung Bersama Sejahtera serta peraturan yang menyangkut</t>
   </si>
   <si>
     <t>bisnis perusahaan</t>
@@ -193,9 +190,6 @@
     <t>InternalConnection</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Corporate Culture PT. XYZ</t>
   </si>
   <si>
@@ -217,16 +211,13 @@
     <t>TugasPokokSpecificMoved</t>
   </si>
   <si>
-    <t>1.</t>
-  </si>
-  <si>
     <t>ExternalXYZConnection</t>
   </si>
   <si>
-    <t>2.</t>
-  </si>
-  <si>
-    <t>3.</t>
+    <t>ExternalConnection</t>
+  </si>
+  <si>
+    <t>XYZ serta peraturan yang menyangkut</t>
   </si>
 </sst>
 </file>
@@ -623,7 +614,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1056,6 +1047,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1065,6 +1065,63 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1083,71 +1140,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1628,37 +1625,37 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="170" t="s">
+      <c r="M2" s="167" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="171"/>
-      <c r="O2" s="171"/>
-      <c r="P2" s="171"/>
-      <c r="Q2" s="171"/>
-      <c r="R2" s="171"/>
-      <c r="S2" s="171"/>
-      <c r="T2" s="171"/>
-      <c r="U2" s="171"/>
-      <c r="V2" s="171"/>
-      <c r="W2" s="171"/>
-      <c r="X2" s="171"/>
-      <c r="Y2" s="171"/>
-      <c r="Z2" s="171"/>
-      <c r="AA2" s="171"/>
-      <c r="AB2" s="171"/>
-      <c r="AC2" s="171"/>
-      <c r="AD2" s="171"/>
-      <c r="AE2" s="171"/>
-      <c r="AF2" s="171"/>
-      <c r="AG2" s="171"/>
-      <c r="AH2" s="171"/>
-      <c r="AI2" s="171"/>
-      <c r="AJ2" s="171"/>
-      <c r="AK2" s="171"/>
-      <c r="AL2" s="171"/>
-      <c r="AM2" s="171"/>
-      <c r="AN2" s="171"/>
-      <c r="AO2" s="172"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="168"/>
+      <c r="R2" s="168"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="168"/>
+      <c r="U2" s="168"/>
+      <c r="V2" s="168"/>
+      <c r="W2" s="168"/>
+      <c r="X2" s="168"/>
+      <c r="Y2" s="168"/>
+      <c r="Z2" s="168"/>
+      <c r="AA2" s="168"/>
+      <c r="AB2" s="168"/>
+      <c r="AC2" s="168"/>
+      <c r="AD2" s="168"/>
+      <c r="AE2" s="168"/>
+      <c r="AF2" s="168"/>
+      <c r="AG2" s="168"/>
+      <c r="AH2" s="168"/>
+      <c r="AI2" s="168"/>
+      <c r="AJ2" s="168"/>
+      <c r="AK2" s="168"/>
+      <c r="AL2" s="168"/>
+      <c r="AM2" s="168"/>
+      <c r="AN2" s="168"/>
+      <c r="AO2" s="169"/>
       <c r="AP2" s="133"/>
       <c r="AQ2" s="134" t="s">
         <v>1</v>
@@ -1671,7 +1668,7 @@
         <v>2</v>
       </c>
       <c r="AW2" s="135" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AX2" s="134"/>
       <c r="AY2" s="134"/>
@@ -1692,35 +1689,35 @@
     <row r="3" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="L3" s="8"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="174"/>
-      <c r="P3" s="174"/>
-      <c r="Q3" s="174"/>
-      <c r="R3" s="174"/>
-      <c r="S3" s="174"/>
-      <c r="T3" s="174"/>
-      <c r="U3" s="174"/>
-      <c r="V3" s="174"/>
-      <c r="W3" s="174"/>
-      <c r="X3" s="174"/>
-      <c r="Y3" s="174"/>
-      <c r="Z3" s="174"/>
-      <c r="AA3" s="174"/>
-      <c r="AB3" s="174"/>
-      <c r="AC3" s="174"/>
-      <c r="AD3" s="174"/>
-      <c r="AE3" s="174"/>
-      <c r="AF3" s="174"/>
-      <c r="AG3" s="174"/>
-      <c r="AH3" s="174"/>
-      <c r="AI3" s="174"/>
-      <c r="AJ3" s="174"/>
-      <c r="AK3" s="174"/>
-      <c r="AL3" s="174"/>
-      <c r="AM3" s="174"/>
-      <c r="AN3" s="174"/>
-      <c r="AO3" s="175"/>
+      <c r="M3" s="170"/>
+      <c r="N3" s="171"/>
+      <c r="O3" s="171"/>
+      <c r="P3" s="171"/>
+      <c r="Q3" s="171"/>
+      <c r="R3" s="171"/>
+      <c r="S3" s="171"/>
+      <c r="T3" s="171"/>
+      <c r="U3" s="171"/>
+      <c r="V3" s="171"/>
+      <c r="W3" s="171"/>
+      <c r="X3" s="171"/>
+      <c r="Y3" s="171"/>
+      <c r="Z3" s="171"/>
+      <c r="AA3" s="171"/>
+      <c r="AB3" s="171"/>
+      <c r="AC3" s="171"/>
+      <c r="AD3" s="171"/>
+      <c r="AE3" s="171"/>
+      <c r="AF3" s="171"/>
+      <c r="AG3" s="171"/>
+      <c r="AH3" s="171"/>
+      <c r="AI3" s="171"/>
+      <c r="AJ3" s="171"/>
+      <c r="AK3" s="171"/>
+      <c r="AL3" s="171"/>
+      <c r="AM3" s="171"/>
+      <c r="AN3" s="171"/>
+      <c r="AO3" s="172"/>
       <c r="AP3" s="137"/>
       <c r="AQ3" s="138"/>
       <c r="AR3" s="138"/>
@@ -1747,35 +1744,35 @@
     <row r="4" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="174"/>
-      <c r="Q4" s="174"/>
-      <c r="R4" s="174"/>
-      <c r="S4" s="174"/>
-      <c r="T4" s="174"/>
-      <c r="U4" s="174"/>
-      <c r="V4" s="174"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="174"/>
-      <c r="Y4" s="174"/>
-      <c r="Z4" s="174"/>
-      <c r="AA4" s="174"/>
-      <c r="AB4" s="174"/>
-      <c r="AC4" s="174"/>
-      <c r="AD4" s="174"/>
-      <c r="AE4" s="174"/>
-      <c r="AF4" s="174"/>
-      <c r="AG4" s="174"/>
-      <c r="AH4" s="174"/>
-      <c r="AI4" s="174"/>
-      <c r="AJ4" s="174"/>
-      <c r="AK4" s="174"/>
-      <c r="AL4" s="174"/>
-      <c r="AM4" s="174"/>
-      <c r="AN4" s="174"/>
-      <c r="AO4" s="175"/>
+      <c r="M4" s="170"/>
+      <c r="N4" s="171"/>
+      <c r="O4" s="171"/>
+      <c r="P4" s="171"/>
+      <c r="Q4" s="171"/>
+      <c r="R4" s="171"/>
+      <c r="S4" s="171"/>
+      <c r="T4" s="171"/>
+      <c r="U4" s="171"/>
+      <c r="V4" s="171"/>
+      <c r="W4" s="171"/>
+      <c r="X4" s="171"/>
+      <c r="Y4" s="171"/>
+      <c r="Z4" s="171"/>
+      <c r="AA4" s="171"/>
+      <c r="AB4" s="171"/>
+      <c r="AC4" s="171"/>
+      <c r="AD4" s="171"/>
+      <c r="AE4" s="171"/>
+      <c r="AF4" s="171"/>
+      <c r="AG4" s="171"/>
+      <c r="AH4" s="171"/>
+      <c r="AI4" s="171"/>
+      <c r="AJ4" s="171"/>
+      <c r="AK4" s="171"/>
+      <c r="AL4" s="171"/>
+      <c r="AM4" s="171"/>
+      <c r="AN4" s="171"/>
+      <c r="AO4" s="172"/>
       <c r="AP4" s="137"/>
       <c r="AQ4" s="138" t="s">
         <v>3</v>
@@ -1788,7 +1785,7 @@
         <v>2</v>
       </c>
       <c r="AW4" s="139" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AX4" s="138"/>
       <c r="AY4" s="138"/>
@@ -1818,35 +1815,35 @@
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="177"/>
-      <c r="O5" s="177"/>
-      <c r="P5" s="177"/>
-      <c r="Q5" s="177"/>
-      <c r="R5" s="177"/>
-      <c r="S5" s="177"/>
-      <c r="T5" s="177"/>
-      <c r="U5" s="177"/>
-      <c r="V5" s="177"/>
-      <c r="W5" s="177"/>
-      <c r="X5" s="177"/>
-      <c r="Y5" s="177"/>
-      <c r="Z5" s="177"/>
-      <c r="AA5" s="177"/>
-      <c r="AB5" s="177"/>
-      <c r="AC5" s="177"/>
-      <c r="AD5" s="177"/>
-      <c r="AE5" s="177"/>
-      <c r="AF5" s="177"/>
-      <c r="AG5" s="177"/>
-      <c r="AH5" s="177"/>
-      <c r="AI5" s="177"/>
-      <c r="AJ5" s="177"/>
-      <c r="AK5" s="177"/>
-      <c r="AL5" s="177"/>
-      <c r="AM5" s="177"/>
-      <c r="AN5" s="177"/>
-      <c r="AO5" s="178"/>
+      <c r="M5" s="173"/>
+      <c r="N5" s="174"/>
+      <c r="O5" s="174"/>
+      <c r="P5" s="174"/>
+      <c r="Q5" s="174"/>
+      <c r="R5" s="174"/>
+      <c r="S5" s="174"/>
+      <c r="T5" s="174"/>
+      <c r="U5" s="174"/>
+      <c r="V5" s="174"/>
+      <c r="W5" s="174"/>
+      <c r="X5" s="174"/>
+      <c r="Y5" s="174"/>
+      <c r="Z5" s="174"/>
+      <c r="AA5" s="174"/>
+      <c r="AB5" s="174"/>
+      <c r="AC5" s="174"/>
+      <c r="AD5" s="174"/>
+      <c r="AE5" s="174"/>
+      <c r="AF5" s="174"/>
+      <c r="AG5" s="174"/>
+      <c r="AH5" s="174"/>
+      <c r="AI5" s="174"/>
+      <c r="AJ5" s="174"/>
+      <c r="AK5" s="174"/>
+      <c r="AL5" s="174"/>
+      <c r="AM5" s="174"/>
+      <c r="AN5" s="174"/>
+      <c r="AO5" s="175"/>
       <c r="AP5" s="141"/>
       <c r="AQ5" s="142" t="s">
         <v>4</v>
@@ -1859,7 +1856,7 @@
         <v>2</v>
       </c>
       <c r="AW5" s="106" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AX5" s="142"/>
       <c r="AY5" s="142"/>
@@ -2009,99 +2006,99 @@
       <c r="BP7" s="22"/>
     </row>
     <row r="8" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="152" t="s">
+      <c r="B8" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="153"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153"/>
-      <c r="F8" s="153"/>
-      <c r="G8" s="153"/>
-      <c r="H8" s="153"/>
-      <c r="I8" s="153"/>
-      <c r="J8" s="153"/>
-      <c r="K8" s="153"/>
-      <c r="L8" s="153"/>
-      <c r="M8" s="153"/>
-      <c r="N8" s="153"/>
-      <c r="O8" s="153"/>
-      <c r="P8" s="153"/>
-      <c r="Q8" s="153"/>
-      <c r="R8" s="153"/>
-      <c r="S8" s="153"/>
-      <c r="T8" s="153"/>
-      <c r="U8" s="153"/>
-      <c r="V8" s="153"/>
-      <c r="W8" s="154"/>
-      <c r="X8" s="152" t="s">
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="156"/>
+      <c r="H8" s="156"/>
+      <c r="I8" s="156"/>
+      <c r="J8" s="156"/>
+      <c r="K8" s="156"/>
+      <c r="L8" s="156"/>
+      <c r="M8" s="156"/>
+      <c r="N8" s="156"/>
+      <c r="O8" s="156"/>
+      <c r="P8" s="156"/>
+      <c r="Q8" s="156"/>
+      <c r="R8" s="156"/>
+      <c r="S8" s="156"/>
+      <c r="T8" s="156"/>
+      <c r="U8" s="156"/>
+      <c r="V8" s="156"/>
+      <c r="W8" s="157"/>
+      <c r="X8" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="Y8" s="153"/>
-      <c r="Z8" s="153"/>
-      <c r="AA8" s="153"/>
-      <c r="AB8" s="153"/>
-      <c r="AC8" s="153"/>
-      <c r="AD8" s="153"/>
-      <c r="AE8" s="153"/>
-      <c r="AF8" s="153"/>
-      <c r="AG8" s="153"/>
-      <c r="AH8" s="153"/>
-      <c r="AI8" s="153"/>
-      <c r="AJ8" s="153"/>
-      <c r="AK8" s="153"/>
-      <c r="AL8" s="153"/>
-      <c r="AM8" s="153"/>
-      <c r="AN8" s="153"/>
-      <c r="AO8" s="154"/>
+      <c r="Y8" s="156"/>
+      <c r="Z8" s="156"/>
+      <c r="AA8" s="156"/>
+      <c r="AB8" s="156"/>
+      <c r="AC8" s="156"/>
+      <c r="AD8" s="156"/>
+      <c r="AE8" s="156"/>
+      <c r="AF8" s="156"/>
+      <c r="AG8" s="156"/>
+      <c r="AH8" s="156"/>
+      <c r="AI8" s="156"/>
+      <c r="AJ8" s="156"/>
+      <c r="AK8" s="156"/>
+      <c r="AL8" s="156"/>
+      <c r="AM8" s="156"/>
+      <c r="AN8" s="156"/>
+      <c r="AO8" s="157"/>
       <c r="AP8" s="24"/>
-      <c r="AQ8" s="152" t="s">
+      <c r="AQ8" s="155" t="s">
         <v>7</v>
       </c>
-      <c r="AR8" s="153"/>
-      <c r="AS8" s="153"/>
-      <c r="AT8" s="153"/>
-      <c r="AU8" s="153"/>
-      <c r="AV8" s="153"/>
-      <c r="AW8" s="153"/>
-      <c r="AX8" s="153"/>
-      <c r="AY8" s="153"/>
-      <c r="AZ8" s="153"/>
-      <c r="BA8" s="153"/>
-      <c r="BB8" s="153"/>
-      <c r="BC8" s="153"/>
-      <c r="BD8" s="153"/>
-      <c r="BE8" s="153"/>
-      <c r="BF8" s="153"/>
-      <c r="BG8" s="153"/>
-      <c r="BH8" s="153"/>
-      <c r="BI8" s="153"/>
-      <c r="BJ8" s="153"/>
-      <c r="BK8" s="154"/>
+      <c r="AR8" s="156"/>
+      <c r="AS8" s="156"/>
+      <c r="AT8" s="156"/>
+      <c r="AU8" s="156"/>
+      <c r="AV8" s="156"/>
+      <c r="AW8" s="156"/>
+      <c r="AX8" s="156"/>
+      <c r="AY8" s="156"/>
+      <c r="AZ8" s="156"/>
+      <c r="BA8" s="156"/>
+      <c r="BB8" s="156"/>
+      <c r="BC8" s="156"/>
+      <c r="BD8" s="156"/>
+      <c r="BE8" s="156"/>
+      <c r="BF8" s="156"/>
+      <c r="BG8" s="156"/>
+      <c r="BH8" s="156"/>
+      <c r="BI8" s="156"/>
+      <c r="BJ8" s="156"/>
+      <c r="BK8" s="157"/>
       <c r="BL8" s="1"/>
       <c r="BN8" s="22"/>
     </row>
     <row r="9" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="7"/>
-      <c r="X9" s="161" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y9" s="162"/>
-      <c r="Z9" s="162"/>
-      <c r="AA9" s="162"/>
-      <c r="AB9" s="162"/>
-      <c r="AC9" s="162"/>
-      <c r="AD9" s="162"/>
-      <c r="AE9" s="162"/>
-      <c r="AF9" s="162"/>
-      <c r="AG9" s="162"/>
-      <c r="AH9" s="162"/>
-      <c r="AI9" s="162"/>
-      <c r="AJ9" s="162"/>
-      <c r="AK9" s="162"/>
-      <c r="AL9" s="162"/>
-      <c r="AM9" s="162"/>
-      <c r="AN9" s="162"/>
-      <c r="AO9" s="163"/>
+      <c r="X9" s="158" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y9" s="159"/>
+      <c r="Z9" s="159"/>
+      <c r="AA9" s="159"/>
+      <c r="AB9" s="159"/>
+      <c r="AC9" s="159"/>
+      <c r="AD9" s="159"/>
+      <c r="AE9" s="159"/>
+      <c r="AF9" s="159"/>
+      <c r="AG9" s="159"/>
+      <c r="AH9" s="159"/>
+      <c r="AI9" s="159"/>
+      <c r="AJ9" s="159"/>
+      <c r="AK9" s="159"/>
+      <c r="AL9" s="159"/>
+      <c r="AM9" s="159"/>
+      <c r="AN9" s="159"/>
+      <c r="AO9" s="160"/>
       <c r="AP9" s="7"/>
       <c r="AQ9" s="107" t="s">
         <v>8</v>
@@ -2114,24 +2111,24 @@
     </row>
     <row r="10" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="7"/>
-      <c r="X10" s="164"/>
-      <c r="Y10" s="165"/>
-      <c r="Z10" s="165"/>
-      <c r="AA10" s="165"/>
-      <c r="AB10" s="165"/>
-      <c r="AC10" s="165"/>
-      <c r="AD10" s="165"/>
-      <c r="AE10" s="165"/>
-      <c r="AF10" s="165"/>
-      <c r="AG10" s="165"/>
-      <c r="AH10" s="165"/>
-      <c r="AI10" s="165"/>
-      <c r="AJ10" s="165"/>
-      <c r="AK10" s="165"/>
-      <c r="AL10" s="165"/>
-      <c r="AM10" s="165"/>
-      <c r="AN10" s="165"/>
-      <c r="AO10" s="166"/>
+      <c r="X10" s="161"/>
+      <c r="Y10" s="162"/>
+      <c r="Z10" s="162"/>
+      <c r="AA10" s="162"/>
+      <c r="AB10" s="162"/>
+      <c r="AC10" s="162"/>
+      <c r="AD10" s="162"/>
+      <c r="AE10" s="162"/>
+      <c r="AF10" s="162"/>
+      <c r="AG10" s="162"/>
+      <c r="AH10" s="162"/>
+      <c r="AI10" s="162"/>
+      <c r="AJ10" s="162"/>
+      <c r="AK10" s="162"/>
+      <c r="AL10" s="162"/>
+      <c r="AM10" s="162"/>
+      <c r="AN10" s="162"/>
+      <c r="AO10" s="163"/>
       <c r="AP10" s="26"/>
       <c r="AQ10" s="27"/>
       <c r="AR10" s="28"/>
@@ -2142,24 +2139,24 @@
     <row r="11" spans="2:68" ht="16.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="7"/>
       <c r="W11" s="8"/>
-      <c r="X11" s="167"/>
-      <c r="Y11" s="168"/>
-      <c r="Z11" s="168"/>
-      <c r="AA11" s="168"/>
-      <c r="AB11" s="168"/>
-      <c r="AC11" s="168"/>
-      <c r="AD11" s="168"/>
-      <c r="AE11" s="168"/>
-      <c r="AF11" s="168"/>
-      <c r="AG11" s="168"/>
-      <c r="AH11" s="168"/>
-      <c r="AI11" s="168"/>
-      <c r="AJ11" s="168"/>
-      <c r="AK11" s="168"/>
-      <c r="AL11" s="168"/>
-      <c r="AM11" s="168"/>
-      <c r="AN11" s="168"/>
-      <c r="AO11" s="169"/>
+      <c r="X11" s="164"/>
+      <c r="Y11" s="165"/>
+      <c r="Z11" s="165"/>
+      <c r="AA11" s="165"/>
+      <c r="AB11" s="165"/>
+      <c r="AC11" s="165"/>
+      <c r="AD11" s="165"/>
+      <c r="AE11" s="165"/>
+      <c r="AF11" s="165"/>
+      <c r="AG11" s="165"/>
+      <c r="AH11" s="165"/>
+      <c r="AI11" s="165"/>
+      <c r="AJ11" s="165"/>
+      <c r="AK11" s="165"/>
+      <c r="AL11" s="165"/>
+      <c r="AM11" s="165"/>
+      <c r="AN11" s="165"/>
+      <c r="AO11" s="166"/>
       <c r="AP11" s="26"/>
       <c r="AQ11" s="30"/>
       <c r="AR11" s="59"/>
@@ -2171,26 +2168,26 @@
     <row r="12" spans="2:68" ht="16.7" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="7"/>
       <c r="W12" s="8"/>
-      <c r="X12" s="152" t="s">
+      <c r="X12" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="Y12" s="153"/>
-      <c r="Z12" s="153"/>
-      <c r="AA12" s="153"/>
-      <c r="AB12" s="153"/>
-      <c r="AC12" s="153"/>
-      <c r="AD12" s="153"/>
-      <c r="AE12" s="153"/>
-      <c r="AF12" s="153"/>
-      <c r="AG12" s="153"/>
-      <c r="AH12" s="153"/>
-      <c r="AI12" s="153"/>
-      <c r="AJ12" s="153"/>
-      <c r="AK12" s="153"/>
-      <c r="AL12" s="153"/>
-      <c r="AM12" s="153"/>
-      <c r="AN12" s="153"/>
-      <c r="AO12" s="154"/>
+      <c r="Y12" s="156"/>
+      <c r="Z12" s="156"/>
+      <c r="AA12" s="156"/>
+      <c r="AB12" s="156"/>
+      <c r="AC12" s="156"/>
+      <c r="AD12" s="156"/>
+      <c r="AE12" s="156"/>
+      <c r="AF12" s="156"/>
+      <c r="AG12" s="156"/>
+      <c r="AH12" s="156"/>
+      <c r="AI12" s="156"/>
+      <c r="AJ12" s="156"/>
+      <c r="AK12" s="156"/>
+      <c r="AL12" s="156"/>
+      <c r="AM12" s="156"/>
+      <c r="AN12" s="156"/>
+      <c r="AO12" s="157"/>
       <c r="AP12" s="26"/>
       <c r="AQ12" s="108" t="s">
         <v>10</v>
@@ -2302,7 +2299,7 @@
       <c r="AO15" s="22"/>
       <c r="AP15" s="26"/>
       <c r="AQ15" s="108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AR15" s="53"/>
       <c r="AS15" s="53"/>
@@ -2522,7 +2519,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="106" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N22" s="11"/>
       <c r="O22" s="11"/>
@@ -2577,70 +2574,70 @@
       <c r="BN22" s="22"/>
     </row>
     <row r="23" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="152" t="s">
+      <c r="B23" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="153"/>
-      <c r="F23" s="153"/>
-      <c r="G23" s="153"/>
-      <c r="H23" s="153"/>
-      <c r="I23" s="153"/>
-      <c r="J23" s="153"/>
-      <c r="K23" s="153"/>
-      <c r="L23" s="153"/>
-      <c r="M23" s="153"/>
-      <c r="N23" s="153"/>
-      <c r="O23" s="153"/>
-      <c r="P23" s="153"/>
-      <c r="Q23" s="153"/>
-      <c r="R23" s="153"/>
-      <c r="S23" s="153"/>
-      <c r="T23" s="153"/>
-      <c r="U23" s="153"/>
-      <c r="V23" s="153"/>
-      <c r="W23" s="153"/>
-      <c r="X23" s="153"/>
-      <c r="Y23" s="153"/>
-      <c r="Z23" s="153"/>
-      <c r="AA23" s="153"/>
-      <c r="AB23" s="153"/>
-      <c r="AC23" s="153"/>
-      <c r="AD23" s="153"/>
-      <c r="AE23" s="153"/>
-      <c r="AF23" s="153"/>
-      <c r="AG23" s="153"/>
-      <c r="AH23" s="153"/>
-      <c r="AI23" s="153"/>
-      <c r="AJ23" s="153"/>
-      <c r="AK23" s="153"/>
-      <c r="AL23" s="153"/>
-      <c r="AM23" s="153"/>
-      <c r="AN23" s="153"/>
-      <c r="AO23" s="153"/>
-      <c r="AP23" s="153"/>
-      <c r="AQ23" s="153"/>
-      <c r="AR23" s="153"/>
-      <c r="AS23" s="153"/>
-      <c r="AT23" s="153"/>
-      <c r="AU23" s="153"/>
-      <c r="AV23" s="153"/>
-      <c r="AW23" s="153"/>
-      <c r="AX23" s="153"/>
-      <c r="AY23" s="153"/>
-      <c r="AZ23" s="153"/>
-      <c r="BA23" s="153"/>
-      <c r="BB23" s="153"/>
-      <c r="BC23" s="153"/>
-      <c r="BD23" s="153"/>
-      <c r="BE23" s="153"/>
-      <c r="BF23" s="153"/>
-      <c r="BG23" s="153"/>
-      <c r="BH23" s="153"/>
-      <c r="BI23" s="153"/>
-      <c r="BJ23" s="153"/>
-      <c r="BK23" s="154"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="156"/>
+      <c r="H23" s="156"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="156"/>
+      <c r="K23" s="156"/>
+      <c r="L23" s="156"/>
+      <c r="M23" s="156"/>
+      <c r="N23" s="156"/>
+      <c r="O23" s="156"/>
+      <c r="P23" s="156"/>
+      <c r="Q23" s="156"/>
+      <c r="R23" s="156"/>
+      <c r="S23" s="156"/>
+      <c r="T23" s="156"/>
+      <c r="U23" s="156"/>
+      <c r="V23" s="156"/>
+      <c r="W23" s="156"/>
+      <c r="X23" s="156"/>
+      <c r="Y23" s="156"/>
+      <c r="Z23" s="156"/>
+      <c r="AA23" s="156"/>
+      <c r="AB23" s="156"/>
+      <c r="AC23" s="156"/>
+      <c r="AD23" s="156"/>
+      <c r="AE23" s="156"/>
+      <c r="AF23" s="156"/>
+      <c r="AG23" s="156"/>
+      <c r="AH23" s="156"/>
+      <c r="AI23" s="156"/>
+      <c r="AJ23" s="156"/>
+      <c r="AK23" s="156"/>
+      <c r="AL23" s="156"/>
+      <c r="AM23" s="156"/>
+      <c r="AN23" s="156"/>
+      <c r="AO23" s="156"/>
+      <c r="AP23" s="156"/>
+      <c r="AQ23" s="156"/>
+      <c r="AR23" s="156"/>
+      <c r="AS23" s="156"/>
+      <c r="AT23" s="156"/>
+      <c r="AU23" s="156"/>
+      <c r="AV23" s="156"/>
+      <c r="AW23" s="156"/>
+      <c r="AX23" s="156"/>
+      <c r="AY23" s="156"/>
+      <c r="AZ23" s="156"/>
+      <c r="BA23" s="156"/>
+      <c r="BB23" s="156"/>
+      <c r="BC23" s="156"/>
+      <c r="BD23" s="156"/>
+      <c r="BE23" s="156"/>
+      <c r="BF23" s="156"/>
+      <c r="BG23" s="156"/>
+      <c r="BH23" s="156"/>
+      <c r="BI23" s="156"/>
+      <c r="BJ23" s="156"/>
+      <c r="BK23" s="157"/>
     </row>
     <row r="24" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B24" s="43" t="s">
@@ -2715,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="51"/>
@@ -2756,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="AR25" s="55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AY25" s="39"/>
       <c r="BK25" s="8"/>
@@ -2768,7 +2765,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="51"/>
       <c r="F26" s="51"/>
@@ -2793,7 +2790,7 @@
         <v>2</v>
       </c>
       <c r="AR26" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AY26" s="39"/>
       <c r="BK26" s="8"/>
@@ -2805,7 +2802,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E27" s="51"/>
       <c r="F27" s="51"/>
@@ -2858,7 +2855,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" s="56"/>
       <c r="E28" s="51"/>
@@ -2899,7 +2896,7 @@
         <v>4</v>
       </c>
       <c r="AR28" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AS28" s="58"/>
       <c r="AU28" s="22"/>
@@ -2912,7 +2909,7 @@
     <row r="29" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="84"/>
       <c r="C29" s="104" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" s="56"/>
       <c r="E29" s="51"/>
@@ -2951,7 +2948,7 @@
       <c r="AP29" s="7"/>
       <c r="AQ29" s="57"/>
       <c r="AR29" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AS29" s="58"/>
       <c r="AU29" s="22"/>
@@ -3090,7 +3087,7 @@
     </row>
     <row r="33" spans="1:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="148" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C33" s="35"/>
       <c r="D33" s="22"/>
@@ -3328,7 +3325,7 @@
       <c r="BK40" s="8"/>
     </row>
     <row r="41" spans="1:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="181"/>
+      <c r="B41" s="153"/>
       <c r="C41" s="104"/>
       <c r="D41" s="29"/>
       <c r="F41" s="1"/>
@@ -3348,80 +3345,80 @@
       <c r="T41" s="1"/>
       <c r="AO41" s="8"/>
       <c r="AP41" s="40"/>
-      <c r="AQ41" s="182"/>
+      <c r="AQ41" s="154"/>
       <c r="AR41" s="35"/>
       <c r="BK41" s="8"/>
     </row>
     <row r="42" spans="1:68" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="180"/>
+      <c r="B42" s="152"/>
       <c r="C42" s="67"/>
       <c r="D42" s="33"/>
       <c r="E42" s="61"/>
     </row>
     <row r="43" spans="1:68" s="1" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
-      <c r="B43" s="157"/>
-      <c r="C43" s="157"/>
-      <c r="D43" s="157"/>
-      <c r="E43" s="157"/>
-      <c r="F43" s="157"/>
-      <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="157"/>
-      <c r="K43" s="157"/>
-      <c r="L43" s="157"/>
-      <c r="M43" s="157"/>
-      <c r="N43" s="157"/>
-      <c r="O43" s="157"/>
-      <c r="P43" s="157"/>
-      <c r="Q43" s="157"/>
-      <c r="R43" s="157"/>
-      <c r="S43" s="157"/>
-      <c r="T43" s="157"/>
-      <c r="U43" s="157"/>
-      <c r="V43" s="157"/>
-      <c r="W43" s="157"/>
-      <c r="X43" s="157"/>
-      <c r="Y43" s="157"/>
-      <c r="Z43" s="157"/>
-      <c r="AA43" s="157"/>
-      <c r="AB43" s="157"/>
-      <c r="AC43" s="157"/>
-      <c r="AD43" s="157"/>
-      <c r="AE43" s="157"/>
-      <c r="AF43" s="157"/>
-      <c r="AG43" s="157"/>
-      <c r="AH43" s="157"/>
-      <c r="AI43" s="157"/>
-      <c r="AJ43" s="157"/>
-      <c r="AK43" s="157"/>
-      <c r="AL43" s="157"/>
-      <c r="AM43" s="157"/>
-      <c r="AN43" s="157"/>
-      <c r="AO43" s="157"/>
-      <c r="AP43" s="157"/>
-      <c r="AQ43" s="157"/>
-      <c r="AR43" s="157"/>
-      <c r="AS43" s="157"/>
-      <c r="AT43" s="157"/>
-      <c r="AU43" s="157"/>
-      <c r="AV43" s="157"/>
-      <c r="AW43" s="157"/>
-      <c r="AX43" s="157"/>
-      <c r="AY43" s="157"/>
-      <c r="AZ43" s="157"/>
-      <c r="BA43" s="157"/>
-      <c r="BB43" s="157"/>
-      <c r="BC43" s="157"/>
-      <c r="BD43" s="157"/>
-      <c r="BE43" s="157"/>
-      <c r="BF43" s="157"/>
-      <c r="BG43" s="157"/>
-      <c r="BH43" s="157"/>
-      <c r="BI43" s="157"/>
-      <c r="BJ43" s="157"/>
-      <c r="BK43" s="157"/>
+      <c r="B43" s="179"/>
+      <c r="C43" s="179"/>
+      <c r="D43" s="179"/>
+      <c r="E43" s="179"/>
+      <c r="F43" s="179"/>
+      <c r="G43" s="179"/>
+      <c r="H43" s="179"/>
+      <c r="I43" s="179"/>
+      <c r="J43" s="179"/>
+      <c r="K43" s="179"/>
+      <c r="L43" s="179"/>
+      <c r="M43" s="179"/>
+      <c r="N43" s="179"/>
+      <c r="O43" s="179"/>
+      <c r="P43" s="179"/>
+      <c r="Q43" s="179"/>
+      <c r="R43" s="179"/>
+      <c r="S43" s="179"/>
+      <c r="T43" s="179"/>
+      <c r="U43" s="179"/>
+      <c r="V43" s="179"/>
+      <c r="W43" s="179"/>
+      <c r="X43" s="179"/>
+      <c r="Y43" s="179"/>
+      <c r="Z43" s="179"/>
+      <c r="AA43" s="179"/>
+      <c r="AB43" s="179"/>
+      <c r="AC43" s="179"/>
+      <c r="AD43" s="179"/>
+      <c r="AE43" s="179"/>
+      <c r="AF43" s="179"/>
+      <c r="AG43" s="179"/>
+      <c r="AH43" s="179"/>
+      <c r="AI43" s="179"/>
+      <c r="AJ43" s="179"/>
+      <c r="AK43" s="179"/>
+      <c r="AL43" s="179"/>
+      <c r="AM43" s="179"/>
+      <c r="AN43" s="179"/>
+      <c r="AO43" s="179"/>
+      <c r="AP43" s="179"/>
+      <c r="AQ43" s="179"/>
+      <c r="AR43" s="179"/>
+      <c r="AS43" s="179"/>
+      <c r="AT43" s="179"/>
+      <c r="AU43" s="179"/>
+      <c r="AV43" s="179"/>
+      <c r="AW43" s="179"/>
+      <c r="AX43" s="179"/>
+      <c r="AY43" s="179"/>
+      <c r="AZ43" s="179"/>
+      <c r="BA43" s="179"/>
+      <c r="BB43" s="179"/>
+      <c r="BC43" s="179"/>
+      <c r="BD43" s="179"/>
+      <c r="BE43" s="179"/>
+      <c r="BF43" s="179"/>
+      <c r="BG43" s="179"/>
+      <c r="BH43" s="179"/>
+      <c r="BI43" s="179"/>
+      <c r="BJ43" s="179"/>
+      <c r="BK43" s="179"/>
       <c r="BL43" s="2"/>
     </row>
     <row r="44" spans="1:68" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -3436,37 +3433,37 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="5"/>
-      <c r="M44" s="170" t="s">
+      <c r="M44" s="167" t="s">
         <v>0</v>
       </c>
-      <c r="N44" s="171"/>
-      <c r="O44" s="171"/>
-      <c r="P44" s="171"/>
-      <c r="Q44" s="171"/>
-      <c r="R44" s="171"/>
-      <c r="S44" s="171"/>
-      <c r="T44" s="171"/>
-      <c r="U44" s="171"/>
-      <c r="V44" s="171"/>
-      <c r="W44" s="171"/>
-      <c r="X44" s="171"/>
-      <c r="Y44" s="171"/>
-      <c r="Z44" s="171"/>
-      <c r="AA44" s="171"/>
-      <c r="AB44" s="171"/>
-      <c r="AC44" s="171"/>
-      <c r="AD44" s="171"/>
-      <c r="AE44" s="171"/>
-      <c r="AF44" s="171"/>
-      <c r="AG44" s="171"/>
-      <c r="AH44" s="171"/>
-      <c r="AI44" s="171"/>
-      <c r="AJ44" s="171"/>
-      <c r="AK44" s="171"/>
-      <c r="AL44" s="171"/>
-      <c r="AM44" s="171"/>
-      <c r="AN44" s="171"/>
-      <c r="AO44" s="172"/>
+      <c r="N44" s="168"/>
+      <c r="O44" s="168"/>
+      <c r="P44" s="168"/>
+      <c r="Q44" s="168"/>
+      <c r="R44" s="168"/>
+      <c r="S44" s="168"/>
+      <c r="T44" s="168"/>
+      <c r="U44" s="168"/>
+      <c r="V44" s="168"/>
+      <c r="W44" s="168"/>
+      <c r="X44" s="168"/>
+      <c r="Y44" s="168"/>
+      <c r="Z44" s="168"/>
+      <c r="AA44" s="168"/>
+      <c r="AB44" s="168"/>
+      <c r="AC44" s="168"/>
+      <c r="AD44" s="168"/>
+      <c r="AE44" s="168"/>
+      <c r="AF44" s="168"/>
+      <c r="AG44" s="168"/>
+      <c r="AH44" s="168"/>
+      <c r="AI44" s="168"/>
+      <c r="AJ44" s="168"/>
+      <c r="AK44" s="168"/>
+      <c r="AL44" s="168"/>
+      <c r="AM44" s="168"/>
+      <c r="AN44" s="168"/>
+      <c r="AO44" s="169"/>
       <c r="AP44" s="144"/>
       <c r="AQ44" s="134" t="str">
         <f>$AQ$2</f>
@@ -3503,35 +3500,35 @@
     <row r="45" spans="1:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="L45" s="8"/>
-      <c r="M45" s="173"/>
-      <c r="N45" s="174"/>
-      <c r="O45" s="174"/>
-      <c r="P45" s="174"/>
-      <c r="Q45" s="174"/>
-      <c r="R45" s="174"/>
-      <c r="S45" s="174"/>
-      <c r="T45" s="174"/>
-      <c r="U45" s="174"/>
-      <c r="V45" s="174"/>
-      <c r="W45" s="174"/>
-      <c r="X45" s="174"/>
-      <c r="Y45" s="174"/>
-      <c r="Z45" s="174"/>
-      <c r="AA45" s="174"/>
-      <c r="AB45" s="174"/>
-      <c r="AC45" s="174"/>
-      <c r="AD45" s="174"/>
-      <c r="AE45" s="174"/>
-      <c r="AF45" s="174"/>
-      <c r="AG45" s="174"/>
-      <c r="AH45" s="174"/>
-      <c r="AI45" s="174"/>
-      <c r="AJ45" s="174"/>
-      <c r="AK45" s="174"/>
-      <c r="AL45" s="174"/>
-      <c r="AM45" s="174"/>
-      <c r="AN45" s="174"/>
-      <c r="AO45" s="175"/>
+      <c r="M45" s="170"/>
+      <c r="N45" s="171"/>
+      <c r="O45" s="171"/>
+      <c r="P45" s="171"/>
+      <c r="Q45" s="171"/>
+      <c r="R45" s="171"/>
+      <c r="S45" s="171"/>
+      <c r="T45" s="171"/>
+      <c r="U45" s="171"/>
+      <c r="V45" s="171"/>
+      <c r="W45" s="171"/>
+      <c r="X45" s="171"/>
+      <c r="Y45" s="171"/>
+      <c r="Z45" s="171"/>
+      <c r="AA45" s="171"/>
+      <c r="AB45" s="171"/>
+      <c r="AC45" s="171"/>
+      <c r="AD45" s="171"/>
+      <c r="AE45" s="171"/>
+      <c r="AF45" s="171"/>
+      <c r="AG45" s="171"/>
+      <c r="AH45" s="171"/>
+      <c r="AI45" s="171"/>
+      <c r="AJ45" s="171"/>
+      <c r="AK45" s="171"/>
+      <c r="AL45" s="171"/>
+      <c r="AM45" s="171"/>
+      <c r="AN45" s="171"/>
+      <c r="AO45" s="172"/>
       <c r="AP45" s="145"/>
       <c r="AQ45" s="108" t="str">
         <f>$AQ$4</f>
@@ -3567,35 +3564,35 @@
     <row r="46" spans="1:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="L46" s="8"/>
-      <c r="M46" s="173"/>
-      <c r="N46" s="174"/>
-      <c r="O46" s="174"/>
-      <c r="P46" s="174"/>
-      <c r="Q46" s="174"/>
-      <c r="R46" s="174"/>
-      <c r="S46" s="174"/>
-      <c r="T46" s="174"/>
-      <c r="U46" s="174"/>
-      <c r="V46" s="174"/>
-      <c r="W46" s="174"/>
-      <c r="X46" s="174"/>
-      <c r="Y46" s="174"/>
-      <c r="Z46" s="174"/>
-      <c r="AA46" s="174"/>
-      <c r="AB46" s="174"/>
-      <c r="AC46" s="174"/>
-      <c r="AD46" s="174"/>
-      <c r="AE46" s="174"/>
-      <c r="AF46" s="174"/>
-      <c r="AG46" s="174"/>
-      <c r="AH46" s="174"/>
-      <c r="AI46" s="174"/>
-      <c r="AJ46" s="174"/>
-      <c r="AK46" s="174"/>
-      <c r="AL46" s="174"/>
-      <c r="AM46" s="174"/>
-      <c r="AN46" s="174"/>
-      <c r="AO46" s="175"/>
+      <c r="M46" s="170"/>
+      <c r="N46" s="171"/>
+      <c r="O46" s="171"/>
+      <c r="P46" s="171"/>
+      <c r="Q46" s="171"/>
+      <c r="R46" s="171"/>
+      <c r="S46" s="171"/>
+      <c r="T46" s="171"/>
+      <c r="U46" s="171"/>
+      <c r="V46" s="171"/>
+      <c r="W46" s="171"/>
+      <c r="X46" s="171"/>
+      <c r="Y46" s="171"/>
+      <c r="Z46" s="171"/>
+      <c r="AA46" s="171"/>
+      <c r="AB46" s="171"/>
+      <c r="AC46" s="171"/>
+      <c r="AD46" s="171"/>
+      <c r="AE46" s="171"/>
+      <c r="AF46" s="171"/>
+      <c r="AG46" s="171"/>
+      <c r="AH46" s="171"/>
+      <c r="AI46" s="171"/>
+      <c r="AJ46" s="171"/>
+      <c r="AK46" s="171"/>
+      <c r="AL46" s="171"/>
+      <c r="AM46" s="171"/>
+      <c r="AN46" s="171"/>
+      <c r="AO46" s="172"/>
       <c r="AP46" s="146"/>
       <c r="AQ46" s="138"/>
       <c r="AR46" s="138"/>
@@ -3632,35 +3629,35 @@
       <c r="J47" s="11"/>
       <c r="K47" s="11"/>
       <c r="L47" s="12"/>
-      <c r="M47" s="176"/>
-      <c r="N47" s="177"/>
-      <c r="O47" s="177"/>
-      <c r="P47" s="177"/>
-      <c r="Q47" s="177"/>
-      <c r="R47" s="177"/>
-      <c r="S47" s="177"/>
-      <c r="T47" s="177"/>
-      <c r="U47" s="177"/>
-      <c r="V47" s="177"/>
-      <c r="W47" s="177"/>
-      <c r="X47" s="177"/>
-      <c r="Y47" s="177"/>
-      <c r="Z47" s="177"/>
-      <c r="AA47" s="177"/>
-      <c r="AB47" s="177"/>
-      <c r="AC47" s="177"/>
-      <c r="AD47" s="177"/>
-      <c r="AE47" s="177"/>
-      <c r="AF47" s="177"/>
-      <c r="AG47" s="177"/>
-      <c r="AH47" s="177"/>
-      <c r="AI47" s="177"/>
-      <c r="AJ47" s="177"/>
-      <c r="AK47" s="177"/>
-      <c r="AL47" s="177"/>
-      <c r="AM47" s="177"/>
-      <c r="AN47" s="177"/>
-      <c r="AO47" s="178"/>
+      <c r="M47" s="173"/>
+      <c r="N47" s="174"/>
+      <c r="O47" s="174"/>
+      <c r="P47" s="174"/>
+      <c r="Q47" s="174"/>
+      <c r="R47" s="174"/>
+      <c r="S47" s="174"/>
+      <c r="T47" s="174"/>
+      <c r="U47" s="174"/>
+      <c r="V47" s="174"/>
+      <c r="W47" s="174"/>
+      <c r="X47" s="174"/>
+      <c r="Y47" s="174"/>
+      <c r="Z47" s="174"/>
+      <c r="AA47" s="174"/>
+      <c r="AB47" s="174"/>
+      <c r="AC47" s="174"/>
+      <c r="AD47" s="174"/>
+      <c r="AE47" s="174"/>
+      <c r="AF47" s="174"/>
+      <c r="AG47" s="174"/>
+      <c r="AH47" s="174"/>
+      <c r="AI47" s="174"/>
+      <c r="AJ47" s="174"/>
+      <c r="AK47" s="174"/>
+      <c r="AL47" s="174"/>
+      <c r="AM47" s="174"/>
+      <c r="AN47" s="174"/>
+      <c r="AO47" s="175"/>
       <c r="AP47" s="147"/>
       <c r="AQ47" s="142" t="str">
         <f>$AQ$5</f>
@@ -3763,74 +3760,74 @@
       <c r="BP49" s="22"/>
     </row>
     <row r="50" spans="2:87" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="158" t="s">
+      <c r="B50" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="C50" s="159"/>
-      <c r="D50" s="159"/>
-      <c r="E50" s="159"/>
-      <c r="F50" s="159"/>
-      <c r="G50" s="159"/>
-      <c r="H50" s="159"/>
-      <c r="I50" s="159"/>
-      <c r="J50" s="159"/>
-      <c r="K50" s="159"/>
-      <c r="L50" s="159"/>
-      <c r="M50" s="159"/>
-      <c r="N50" s="159"/>
-      <c r="O50" s="159"/>
-      <c r="P50" s="159"/>
-      <c r="Q50" s="159"/>
-      <c r="R50" s="159"/>
-      <c r="S50" s="159"/>
-      <c r="T50" s="160"/>
+      <c r="C50" s="181"/>
+      <c r="D50" s="181"/>
+      <c r="E50" s="181"/>
+      <c r="F50" s="181"/>
+      <c r="G50" s="181"/>
+      <c r="H50" s="181"/>
+      <c r="I50" s="181"/>
+      <c r="J50" s="181"/>
+      <c r="K50" s="181"/>
+      <c r="L50" s="181"/>
+      <c r="M50" s="181"/>
+      <c r="N50" s="181"/>
+      <c r="O50" s="181"/>
+      <c r="P50" s="181"/>
+      <c r="Q50" s="181"/>
+      <c r="R50" s="181"/>
+      <c r="S50" s="181"/>
+      <c r="T50" s="182"/>
       <c r="U50" s="1"/>
-      <c r="V50" s="158" t="s">
+      <c r="V50" s="180" t="s">
         <v>18</v>
       </c>
-      <c r="W50" s="159"/>
-      <c r="X50" s="159"/>
-      <c r="Y50" s="159"/>
-      <c r="Z50" s="159"/>
-      <c r="AA50" s="159"/>
-      <c r="AB50" s="159"/>
-      <c r="AC50" s="159"/>
-      <c r="AD50" s="159"/>
-      <c r="AE50" s="159"/>
-      <c r="AF50" s="159"/>
-      <c r="AG50" s="159"/>
-      <c r="AH50" s="159"/>
-      <c r="AI50" s="159"/>
-      <c r="AJ50" s="159"/>
-      <c r="AK50" s="159"/>
-      <c r="AL50" s="159"/>
-      <c r="AM50" s="159"/>
-      <c r="AN50" s="159"/>
-      <c r="AO50" s="160"/>
+      <c r="W50" s="181"/>
+      <c r="X50" s="181"/>
+      <c r="Y50" s="181"/>
+      <c r="Z50" s="181"/>
+      <c r="AA50" s="181"/>
+      <c r="AB50" s="181"/>
+      <c r="AC50" s="181"/>
+      <c r="AD50" s="181"/>
+      <c r="AE50" s="181"/>
+      <c r="AF50" s="181"/>
+      <c r="AG50" s="181"/>
+      <c r="AH50" s="181"/>
+      <c r="AI50" s="181"/>
+      <c r="AJ50" s="181"/>
+      <c r="AK50" s="181"/>
+      <c r="AL50" s="181"/>
+      <c r="AM50" s="181"/>
+      <c r="AN50" s="181"/>
+      <c r="AO50" s="182"/>
       <c r="AP50" s="1"/>
-      <c r="AQ50" s="158" t="s">
+      <c r="AQ50" s="180" t="s">
         <v>19</v>
       </c>
-      <c r="AR50" s="159"/>
-      <c r="AS50" s="159"/>
-      <c r="AT50" s="159"/>
-      <c r="AU50" s="159"/>
-      <c r="AV50" s="159"/>
-      <c r="AW50" s="159"/>
-      <c r="AX50" s="159"/>
-      <c r="AY50" s="159"/>
-      <c r="AZ50" s="159"/>
-      <c r="BA50" s="159"/>
-      <c r="BB50" s="159"/>
-      <c r="BC50" s="159"/>
-      <c r="BD50" s="159"/>
-      <c r="BE50" s="159"/>
-      <c r="BF50" s="159"/>
-      <c r="BG50" s="159"/>
-      <c r="BH50" s="159"/>
-      <c r="BI50" s="159"/>
-      <c r="BJ50" s="159"/>
-      <c r="BK50" s="160"/>
+      <c r="AR50" s="181"/>
+      <c r="AS50" s="181"/>
+      <c r="AT50" s="181"/>
+      <c r="AU50" s="181"/>
+      <c r="AV50" s="181"/>
+      <c r="AW50" s="181"/>
+      <c r="AX50" s="181"/>
+      <c r="AY50" s="181"/>
+      <c r="AZ50" s="181"/>
+      <c r="BA50" s="181"/>
+      <c r="BB50" s="181"/>
+      <c r="BC50" s="181"/>
+      <c r="BD50" s="181"/>
+      <c r="BE50" s="181"/>
+      <c r="BF50" s="181"/>
+      <c r="BG50" s="181"/>
+      <c r="BH50" s="181"/>
+      <c r="BI50" s="181"/>
+      <c r="BJ50" s="181"/>
+      <c r="BK50" s="182"/>
       <c r="BN50" s="22"/>
       <c r="BO50" s="23"/>
       <c r="BP50" s="22"/>
@@ -3878,31 +3875,31 @@
       <c r="BI51" s="63"/>
       <c r="BJ51" s="59"/>
       <c r="BK51" s="74"/>
-      <c r="BO51" s="179"/>
-      <c r="BP51" s="179"/>
-      <c r="BQ51" s="179"/>
-      <c r="BR51" s="179"/>
-      <c r="BS51" s="179"/>
-      <c r="BT51" s="179"/>
-      <c r="BU51" s="179"/>
-      <c r="BV51" s="179"/>
-      <c r="BW51" s="179"/>
-      <c r="BX51" s="179"/>
-      <c r="BY51" s="179"/>
-      <c r="BZ51" s="179"/>
-      <c r="CA51" s="179"/>
-      <c r="CB51" s="179"/>
-      <c r="CC51" s="179"/>
-      <c r="CD51" s="179"/>
-      <c r="CE51" s="179"/>
-      <c r="CF51" s="179"/>
-      <c r="CG51" s="179"/>
-      <c r="CH51" s="179"/>
-      <c r="CI51" s="179"/>
+      <c r="BO51" s="176"/>
+      <c r="BP51" s="176"/>
+      <c r="BQ51" s="176"/>
+      <c r="BR51" s="176"/>
+      <c r="BS51" s="176"/>
+      <c r="BT51" s="176"/>
+      <c r="BU51" s="176"/>
+      <c r="BV51" s="176"/>
+      <c r="BW51" s="176"/>
+      <c r="BX51" s="176"/>
+      <c r="BY51" s="176"/>
+      <c r="BZ51" s="176"/>
+      <c r="CA51" s="176"/>
+      <c r="CB51" s="176"/>
+      <c r="CC51" s="176"/>
+      <c r="CD51" s="176"/>
+      <c r="CE51" s="176"/>
+      <c r="CF51" s="176"/>
+      <c r="CG51" s="176"/>
+      <c r="CH51" s="176"/>
+      <c r="CI51" s="176"/>
     </row>
     <row r="52" spans="2:87" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="132" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C52" s="111"/>
       <c r="D52" s="58"/>
@@ -3926,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="W52" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="X52" s="30"/>
       <c r="AO52" s="8"/>
@@ -4086,7 +4083,7 @@
       <c r="AO55" s="8"/>
       <c r="AQ55" s="78"/>
       <c r="AR55" s="76" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="AS55" s="55"/>
       <c r="AT55" s="55"/>
@@ -4133,7 +4130,7 @@
       <c r="AO56" s="8"/>
       <c r="AQ56" s="80"/>
       <c r="AR56" s="76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS56" s="55"/>
       <c r="AT56" s="81"/>
@@ -4182,7 +4179,7 @@
         <v>3</v>
       </c>
       <c r="AR57" s="76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS57" s="81"/>
       <c r="AT57" s="81"/>
@@ -4229,7 +4226,7 @@
       <c r="AO58" s="8"/>
       <c r="AQ58" s="84"/>
       <c r="AR58" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS58" s="81"/>
       <c r="AU58" s="81"/>
@@ -4275,7 +4272,7 @@
         <v>4</v>
       </c>
       <c r="AR59" s="60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT59" s="81"/>
       <c r="AU59" s="81"/>
@@ -4421,23 +4418,23 @@
       <c r="BI62" s="81"/>
       <c r="BK62" s="8"/>
       <c r="BO62" s="1"/>
-      <c r="BP62" s="179"/>
-      <c r="BQ62" s="179"/>
-      <c r="BR62" s="179"/>
-      <c r="BS62" s="179"/>
-      <c r="BT62" s="179"/>
-      <c r="BU62" s="179"/>
-      <c r="BV62" s="179"/>
-      <c r="BW62" s="179"/>
-      <c r="BX62" s="179"/>
-      <c r="BY62" s="179"/>
-      <c r="BZ62" s="179"/>
-      <c r="CA62" s="179"/>
-      <c r="CB62" s="179"/>
-      <c r="CC62" s="179"/>
-      <c r="CD62" s="179"/>
-      <c r="CE62" s="179"/>
-      <c r="CF62" s="179"/>
+      <c r="BP62" s="176"/>
+      <c r="BQ62" s="176"/>
+      <c r="BR62" s="176"/>
+      <c r="BS62" s="176"/>
+      <c r="BT62" s="176"/>
+      <c r="BU62" s="176"/>
+      <c r="BV62" s="176"/>
+      <c r="BW62" s="176"/>
+      <c r="BX62" s="176"/>
+      <c r="BY62" s="176"/>
+      <c r="BZ62" s="176"/>
+      <c r="CA62" s="176"/>
+      <c r="CB62" s="176"/>
+      <c r="CC62" s="176"/>
+      <c r="CD62" s="176"/>
+      <c r="CE62" s="176"/>
+      <c r="CF62" s="176"/>
     </row>
     <row r="63" spans="2:87" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="113"/>
@@ -4545,28 +4542,28 @@
       <c r="R65" s="95"/>
       <c r="S65" s="95"/>
       <c r="T65" s="124"/>
-      <c r="V65" s="152" t="s">
-        <v>28</v>
-      </c>
-      <c r="W65" s="153"/>
-      <c r="X65" s="153"/>
-      <c r="Y65" s="153"/>
-      <c r="Z65" s="153"/>
-      <c r="AA65" s="153"/>
-      <c r="AB65" s="153"/>
-      <c r="AC65" s="153"/>
-      <c r="AD65" s="153"/>
-      <c r="AE65" s="153"/>
-      <c r="AF65" s="153"/>
-      <c r="AG65" s="153"/>
-      <c r="AH65" s="153"/>
-      <c r="AI65" s="153"/>
-      <c r="AJ65" s="153"/>
-      <c r="AK65" s="153"/>
-      <c r="AL65" s="153"/>
-      <c r="AM65" s="153"/>
-      <c r="AN65" s="153"/>
-      <c r="AO65" s="154"/>
+      <c r="V65" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="W65" s="156"/>
+      <c r="X65" s="156"/>
+      <c r="Y65" s="156"/>
+      <c r="Z65" s="156"/>
+      <c r="AA65" s="156"/>
+      <c r="AB65" s="156"/>
+      <c r="AC65" s="156"/>
+      <c r="AD65" s="156"/>
+      <c r="AE65" s="156"/>
+      <c r="AF65" s="156"/>
+      <c r="AG65" s="156"/>
+      <c r="AH65" s="156"/>
+      <c r="AI65" s="156"/>
+      <c r="AJ65" s="156"/>
+      <c r="AK65" s="156"/>
+      <c r="AL65" s="156"/>
+      <c r="AM65" s="156"/>
+      <c r="AN65" s="156"/>
+      <c r="AO65" s="157"/>
       <c r="AP65" s="40"/>
       <c r="AS65" s="81"/>
       <c r="AT65" s="81"/>
@@ -4939,24 +4936,24 @@
       <c r="AO74" s="8"/>
       <c r="AP74" s="8"/>
       <c r="BK74" s="8"/>
-      <c r="BO74" s="179"/>
-      <c r="BP74" s="179"/>
-      <c r="BQ74" s="179"/>
-      <c r="BR74" s="179"/>
-      <c r="BS74" s="179"/>
-      <c r="BT74" s="179"/>
-      <c r="BU74" s="179"/>
-      <c r="BV74" s="179"/>
-      <c r="BW74" s="179"/>
-      <c r="BX74" s="179"/>
-      <c r="BY74" s="179"/>
-      <c r="BZ74" s="179"/>
-      <c r="CA74" s="179"/>
-      <c r="CB74" s="179"/>
-      <c r="CC74" s="179"/>
-      <c r="CD74" s="179"/>
-      <c r="CE74" s="179"/>
-      <c r="CF74" s="179"/>
+      <c r="BO74" s="176"/>
+      <c r="BP74" s="176"/>
+      <c r="BQ74" s="176"/>
+      <c r="BR74" s="176"/>
+      <c r="BS74" s="176"/>
+      <c r="BT74" s="176"/>
+      <c r="BU74" s="176"/>
+      <c r="BV74" s="176"/>
+      <c r="BW74" s="176"/>
+      <c r="BX74" s="176"/>
+      <c r="BY74" s="176"/>
+      <c r="BZ74" s="176"/>
+      <c r="CA74" s="176"/>
+      <c r="CB74" s="176"/>
+      <c r="CC74" s="176"/>
+      <c r="CD74" s="176"/>
+      <c r="CE74" s="176"/>
+      <c r="CF74" s="176"/>
     </row>
     <row r="75" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B75" s="7"/>
@@ -5001,96 +4998,96 @@
       <c r="BK79" s="12"/>
     </row>
     <row r="80" spans="2:84" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="152" t="s">
+      <c r="B80" s="155" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" s="156"/>
+      <c r="D80" s="156"/>
+      <c r="E80" s="156"/>
+      <c r="F80" s="156"/>
+      <c r="G80" s="156"/>
+      <c r="H80" s="156"/>
+      <c r="I80" s="156"/>
+      <c r="J80" s="156"/>
+      <c r="K80" s="156"/>
+      <c r="L80" s="156"/>
+      <c r="M80" s="156"/>
+      <c r="N80" s="156"/>
+      <c r="O80" s="156"/>
+      <c r="P80" s="156"/>
+      <c r="Q80" s="156"/>
+      <c r="R80" s="156"/>
+      <c r="S80" s="156"/>
+      <c r="T80" s="156"/>
+      <c r="U80" s="156"/>
+      <c r="V80" s="156"/>
+      <c r="W80" s="156"/>
+      <c r="X80" s="156"/>
+      <c r="Y80" s="156"/>
+      <c r="Z80" s="156"/>
+      <c r="AA80" s="156"/>
+      <c r="AB80" s="156"/>
+      <c r="AC80" s="156"/>
+      <c r="AD80" s="156"/>
+      <c r="AE80" s="156"/>
+      <c r="AF80" s="156"/>
+      <c r="AG80" s="156"/>
+      <c r="AH80" s="156"/>
+      <c r="AI80" s="156"/>
+      <c r="AJ80" s="156"/>
+      <c r="AK80" s="156"/>
+      <c r="AL80" s="156"/>
+      <c r="AM80" s="156"/>
+      <c r="AN80" s="156"/>
+      <c r="AO80" s="156"/>
+      <c r="AP80" s="156"/>
+      <c r="AQ80" s="156"/>
+      <c r="AR80" s="156"/>
+      <c r="AS80" s="156"/>
+      <c r="AT80" s="156"/>
+      <c r="AU80" s="156"/>
+      <c r="AV80" s="156"/>
+      <c r="AW80" s="156"/>
+      <c r="AX80" s="156"/>
+      <c r="AY80" s="156"/>
+      <c r="AZ80" s="156"/>
+      <c r="BA80" s="156"/>
+      <c r="BB80" s="156"/>
+      <c r="BC80" s="156"/>
+      <c r="BD80" s="156"/>
+      <c r="BE80" s="156"/>
+      <c r="BF80" s="156"/>
+      <c r="BG80" s="156"/>
+      <c r="BH80" s="156"/>
+      <c r="BI80" s="156"/>
+      <c r="BJ80" s="156"/>
+      <c r="BK80" s="157"/>
+    </row>
+    <row r="81" spans="2:63" ht="13.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="177" t="s">
         <v>29</v>
       </c>
-      <c r="C80" s="153"/>
-      <c r="D80" s="153"/>
-      <c r="E80" s="153"/>
-      <c r="F80" s="153"/>
-      <c r="G80" s="153"/>
-      <c r="H80" s="153"/>
-      <c r="I80" s="153"/>
-      <c r="J80" s="153"/>
-      <c r="K80" s="153"/>
-      <c r="L80" s="153"/>
-      <c r="M80" s="153"/>
-      <c r="N80" s="153"/>
-      <c r="O80" s="153"/>
-      <c r="P80" s="153"/>
-      <c r="Q80" s="153"/>
-      <c r="R80" s="153"/>
-      <c r="S80" s="153"/>
-      <c r="T80" s="153"/>
-      <c r="U80" s="153"/>
-      <c r="V80" s="153"/>
-      <c r="W80" s="153"/>
-      <c r="X80" s="153"/>
-      <c r="Y80" s="153"/>
-      <c r="Z80" s="153"/>
-      <c r="AA80" s="153"/>
-      <c r="AB80" s="153"/>
-      <c r="AC80" s="153"/>
-      <c r="AD80" s="153"/>
-      <c r="AE80" s="153"/>
-      <c r="AF80" s="153"/>
-      <c r="AG80" s="153"/>
-      <c r="AH80" s="153"/>
-      <c r="AI80" s="153"/>
-      <c r="AJ80" s="153"/>
-      <c r="AK80" s="153"/>
-      <c r="AL80" s="153"/>
-      <c r="AM80" s="153"/>
-      <c r="AN80" s="153"/>
-      <c r="AO80" s="153"/>
-      <c r="AP80" s="153"/>
-      <c r="AQ80" s="153"/>
-      <c r="AR80" s="153"/>
-      <c r="AS80" s="153"/>
-      <c r="AT80" s="153"/>
-      <c r="AU80" s="153"/>
-      <c r="AV80" s="153"/>
-      <c r="AW80" s="153"/>
-      <c r="AX80" s="153"/>
-      <c r="AY80" s="153"/>
-      <c r="AZ80" s="153"/>
-      <c r="BA80" s="153"/>
-      <c r="BB80" s="153"/>
-      <c r="BC80" s="153"/>
-      <c r="BD80" s="153"/>
-      <c r="BE80" s="153"/>
-      <c r="BF80" s="153"/>
-      <c r="BG80" s="153"/>
-      <c r="BH80" s="153"/>
-      <c r="BI80" s="153"/>
-      <c r="BJ80" s="153"/>
-      <c r="BK80" s="154"/>
-    </row>
-    <row r="81" spans="2:63" ht="13.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="155" t="s">
-        <v>30</v>
-      </c>
-      <c r="C81" s="156"/>
-      <c r="D81" s="156"/>
-      <c r="E81" s="156"/>
-      <c r="F81" s="156"/>
-      <c r="G81" s="156"/>
-      <c r="H81" s="156"/>
-      <c r="I81" s="156"/>
-      <c r="J81" s="156"/>
-      <c r="K81" s="156"/>
-      <c r="L81" s="156"/>
-      <c r="M81" s="156"/>
-      <c r="N81" s="156"/>
-      <c r="O81" s="156"/>
-      <c r="P81" s="156"/>
-      <c r="Q81" s="156"/>
-      <c r="R81" s="156"/>
-      <c r="S81" s="156"/>
-      <c r="T81" s="156"/>
+      <c r="C81" s="178"/>
+      <c r="D81" s="178"/>
+      <c r="E81" s="178"/>
+      <c r="F81" s="178"/>
+      <c r="G81" s="178"/>
+      <c r="H81" s="178"/>
+      <c r="I81" s="178"/>
+      <c r="J81" s="178"/>
+      <c r="K81" s="178"/>
+      <c r="L81" s="178"/>
+      <c r="M81" s="178"/>
+      <c r="N81" s="178"/>
+      <c r="O81" s="178"/>
+      <c r="P81" s="178"/>
+      <c r="Q81" s="178"/>
+      <c r="R81" s="178"/>
+      <c r="S81" s="178"/>
+      <c r="T81" s="178"/>
       <c r="U81" s="4"/>
       <c r="V81" s="90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W81" s="91"/>
       <c r="AQ81" s="4"/>
@@ -5098,7 +5095,7 @@
     </row>
     <row r="82" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B82" s="92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C82" s="51"/>
       <c r="D82" s="51"/>
@@ -5119,18 +5116,18 @@
       <c r="S82" s="51"/>
       <c r="T82" s="51"/>
       <c r="V82" s="51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W82" s="51"/>
       <c r="AQ82" s="93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AR82" s="94"/>
       <c r="BK82" s="8"/>
     </row>
     <row r="83" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B83" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D83" s="95"/>
       <c r="E83" s="95"/>
@@ -5158,12 +5155,10 @@
       <c r="BK83" s="8"/>
     </row>
     <row r="84" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B84" s="149" t="s">
-        <v>56</v>
-      </c>
-      <c r="C84" s="35" t="s">
-        <v>47</v>
-      </c>
+      <c r="B84" s="183" t="s">
+        <v>46</v>
+      </c>
+      <c r="C84" s="59"/>
       <c r="D84" s="59"/>
       <c r="E84" s="95"/>
       <c r="F84" s="95"/>
@@ -5182,12 +5177,10 @@
       <c r="S84" s="95"/>
       <c r="T84" s="95"/>
       <c r="U84" s="59"/>
-      <c r="V84" s="150" t="s">
-        <v>56</v>
-      </c>
-      <c r="W84" s="114" t="s">
-        <v>57</v>
-      </c>
+      <c r="V84" s="114" t="s">
+        <v>54</v>
+      </c>
+      <c r="W84" s="59"/>
       <c r="X84" s="59"/>
       <c r="Y84" s="59"/>
       <c r="Z84" s="59"/>
@@ -5207,22 +5200,16 @@
       <c r="AN84" s="59"/>
       <c r="AO84" s="59"/>
       <c r="AP84" s="59"/>
-      <c r="AQ84" s="150" t="s">
-        <v>56</v>
-      </c>
-      <c r="AR84" s="130" t="s">
-        <v>48</v>
-      </c>
+      <c r="AQ84" s="111" t="s">
+        <v>55</v>
+      </c>
+      <c r="AR84" s="130"/>
       <c r="AS84" s="59"/>
       <c r="BK84" s="8"/>
     </row>
     <row r="85" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B85" s="120" t="s">
-        <v>58</v>
-      </c>
-      <c r="C85" s="35" t="s">
-        <v>48</v>
-      </c>
+      <c r="B85" s="120"/>
+      <c r="C85" s="35"/>
       <c r="D85" s="95"/>
       <c r="E85" s="95"/>
       <c r="F85" s="95"/>
@@ -5241,12 +5228,8 @@
       <c r="S85" s="95"/>
       <c r="T85" s="95"/>
       <c r="U85" s="59"/>
-      <c r="V85" s="150" t="s">
-        <v>58</v>
-      </c>
-      <c r="W85" s="151" t="s">
-        <v>48</v>
-      </c>
+      <c r="V85" s="150"/>
+      <c r="W85" s="151"/>
       <c r="X85" s="59"/>
       <c r="Y85" s="59"/>
       <c r="Z85" s="59"/>
@@ -5266,22 +5249,14 @@
       <c r="AN85" s="59"/>
       <c r="AO85" s="59"/>
       <c r="AP85" s="59"/>
-      <c r="AQ85" s="150" t="s">
-        <v>58</v>
-      </c>
-      <c r="AR85" s="130" t="s">
-        <v>48</v>
-      </c>
+      <c r="AQ85" s="150"/>
+      <c r="AR85" s="130"/>
       <c r="AS85" s="59"/>
       <c r="BK85" s="8"/>
     </row>
     <row r="86" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B86" s="149" t="s">
-        <v>59</v>
-      </c>
-      <c r="C86" s="118" t="s">
-        <v>48</v>
-      </c>
+      <c r="B86" s="149"/>
+      <c r="C86" s="118"/>
       <c r="D86" s="95"/>
       <c r="E86" s="95"/>
       <c r="F86" s="95"/>
@@ -5300,12 +5275,8 @@
       <c r="S86" s="95"/>
       <c r="T86" s="95"/>
       <c r="U86" s="59"/>
-      <c r="V86" s="96" t="s">
-        <v>59</v>
-      </c>
-      <c r="W86" s="151" t="s">
-        <v>48</v>
-      </c>
+      <c r="V86" s="96"/>
+      <c r="W86" s="151"/>
       <c r="X86" s="59"/>
       <c r="Y86" s="59"/>
       <c r="Z86" s="59"/>
@@ -5325,12 +5296,8 @@
       <c r="AN86" s="59"/>
       <c r="AO86" s="59"/>
       <c r="AP86" s="59"/>
-      <c r="AQ86" s="96" t="s">
-        <v>59</v>
-      </c>
-      <c r="AR86" s="130" t="s">
-        <v>48</v>
-      </c>
+      <c r="AQ86" s="96"/>
+      <c r="AR86" s="130"/>
       <c r="AS86" s="59"/>
       <c r="BK86" s="8"/>
     </row>
@@ -5471,7 +5438,9 @@
       <c r="AN89" s="59"/>
       <c r="AO89" s="59"/>
       <c r="AP89" s="53"/>
-      <c r="AQ89" s="9"/>
+      <c r="AQ89" s="184"/>
+      <c r="AR89" s="59"/>
+      <c r="AS89" s="59"/>
       <c r="AX89" s="99"/>
       <c r="BK89" s="8"/>
     </row>
@@ -5595,6 +5564,14 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B80:BK80"/>
+    <mergeCell ref="B81:T81"/>
+    <mergeCell ref="B23:BK23"/>
+    <mergeCell ref="B43:BK43"/>
+    <mergeCell ref="B50:T50"/>
+    <mergeCell ref="V50:AO50"/>
+    <mergeCell ref="AQ50:BK50"/>
+    <mergeCell ref="V65:AO65"/>
     <mergeCell ref="AQ8:BK8"/>
     <mergeCell ref="X9:AO11"/>
     <mergeCell ref="M2:AO5"/>
@@ -5605,14 +5582,6 @@
     <mergeCell ref="X12:AO12"/>
     <mergeCell ref="B8:W8"/>
     <mergeCell ref="X8:AO8"/>
-    <mergeCell ref="B80:BK80"/>
-    <mergeCell ref="B81:T81"/>
-    <mergeCell ref="B23:BK23"/>
-    <mergeCell ref="B43:BK43"/>
-    <mergeCell ref="B50:T50"/>
-    <mergeCell ref="V50:AO50"/>
-    <mergeCell ref="AQ50:BK50"/>
-    <mergeCell ref="V65:AO65"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="3.937007874015748E-2" footer="0.23622047244094491"/>
